--- a/utils/monday_sprint_sprint_2024-26.xlsx
+++ b/utils/monday_sprint_sprint_2024-26.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="140">
   <si>
     <t>Ticket</t>
   </si>
@@ -144,7 +144,7 @@
     <t>30/10/2023</t>
   </si>
   <si>
-    <t>09/05/2026</t>
+    <t>04/05/2026</t>
   </si>
   <si>
     <t>Semana 5</t>
@@ -412,9 +412,6 @@
   </si>
   <si>
     <t>A fazer</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
   </si>
   <si>
     <t>Impedimento</t>
@@ -2874,7 +2871,7 @@
         <v>21</v>
       </c>
       <c r="Q10">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -2903,10 +2900,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>133</v>
+        <v>33</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -2923,19 +2920,19 @@
         <v>34</v>
       </c>
       <c r="M12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="Q12">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
         <v>98</v>
       </c>
@@ -2943,7 +2940,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2953,12 +2950,6 @@
       </c>
       <c r="N13">
         <v>1</v>
-      </c>
-      <c r="P13" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
@@ -2977,7 +2968,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2985,7 +2976,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2993,7 +2984,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3001,7 +2992,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -3012,7 +3003,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3026,7 +3017,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>38</v>
@@ -3040,7 +3031,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>38</v>

--- a/utils/monday_sprint_sprint_2024-26.xlsx
+++ b/utils/monday_sprint_sprint_2024-26.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="165">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>22994</t>
+    <t>5443817656</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,13 +87,13 @@
     <t>02/11/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>07/01/2024</t>
   </si>
   <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>Aberto</t>
+    <t>Não</t>
   </si>
   <si>
     <t>Semana 1</t>
@@ -117,12 +117,12 @@
     <t>26/12/2023</t>
   </si>
   <si>
+    <t>08/01/2024</t>
+  </si>
+  <si>
     <t>Feito</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
     <t>Semana 4</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t>5743567268</t>
   </si>
   <si>
-    <t>23485</t>
+    <t>5703563243</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -150,7 +150,7 @@
     <t>Semana 3</t>
   </si>
   <si>
-    <t>23599</t>
+    <t>5695908624</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Controle de Acessos</t>
@@ -183,31 +183,37 @@
     <t>04/05/2026</t>
   </si>
   <si>
+    <t>5608629982</t>
+  </si>
+  <si>
     <t>Estorno de peças do deposito fabril</t>
   </si>
   <si>
     <t>01/12/2023</t>
   </si>
   <si>
+    <t>5619811145</t>
+  </si>
+  <si>
     <t>Estorno de peças do deposito fabril - Webservice Estorno</t>
   </si>
   <si>
     <t>04/12/2023</t>
   </si>
   <si>
-    <t>23309</t>
+    <t>5702928391</t>
   </si>
   <si>
     <t>Desenvolver Consistência Apontamento de Horas - Apontamento Solda (copy)</t>
   </si>
   <si>
-    <t>23628</t>
+    <t>5695068448</t>
   </si>
   <si>
     <t>Automação de planilha controle Ronda - Análise</t>
   </si>
   <si>
-    <t>23177</t>
+    <t>5532791661</t>
   </si>
   <si>
     <t>Saída Depósito - Expedição</t>
@@ -216,115 +222,139 @@
     <t>17/11/2023</t>
   </si>
   <si>
-    <t>23728</t>
+    <t>06/01/2024</t>
+  </si>
+  <si>
+    <t>5694806898</t>
   </si>
   <si>
     <t>Integração via API Efact</t>
   </si>
   <si>
-    <t>23717</t>
+    <t>5694825193</t>
   </si>
   <si>
     <t>Relatório de NF lançadas</t>
   </si>
   <si>
-    <t>23710</t>
+    <t>5694836096</t>
   </si>
   <si>
     <t>Inclusão de O.C. no PCP</t>
   </si>
   <si>
-    <t>23709</t>
+    <t>5694851675</t>
   </si>
   <si>
     <t>Inclusão colunas no planilhão / Máscara MPS</t>
   </si>
   <si>
-    <t>23685</t>
+    <t>5694864404</t>
   </si>
   <si>
     <t>Inclusao Data Entrega</t>
   </si>
   <si>
-    <t>23663</t>
+    <t>20/12/2023</t>
+  </si>
+  <si>
+    <t>5694874757</t>
   </si>
   <si>
     <t>Tabela de Faturamento fornecedores</t>
   </si>
   <si>
-    <t>23651</t>
+    <t>5695021117</t>
   </si>
   <si>
     <t>Relatório Peso agrupado</t>
   </si>
   <si>
-    <t>23632</t>
+    <t>17/12/2023</t>
+  </si>
+  <si>
+    <t>5695037251</t>
   </si>
   <si>
     <t>Ticket - Alteração da Abertura do Setor 517 em Fluxos de Pré-Produtivo</t>
   </si>
   <si>
-    <t>23629</t>
+    <t>01/01/2024</t>
+  </si>
+  <si>
+    <t>5695046713</t>
   </si>
   <si>
     <t>INVENTÁRIO GERAL DEPOSITO FABRIL</t>
   </si>
   <si>
-    <t>23627</t>
+    <t>30/12/2023</t>
+  </si>
+  <si>
+    <t>5695077916</t>
   </si>
   <si>
     <t>Ticket - Liga Específica para itens não fundidos</t>
   </si>
   <si>
-    <t>23620</t>
+    <t>21/12/2023</t>
+  </si>
+  <si>
+    <t>5695091716</t>
   </si>
   <si>
     <t>BUG - INVENTÁRIO BOX</t>
   </si>
   <si>
-    <t>23617</t>
+    <t>19/12/2023</t>
+  </si>
+  <si>
+    <t>5695841070</t>
   </si>
   <si>
     <t>MPS x Embalagem</t>
   </si>
   <si>
-    <t>23656</t>
+    <t>25/12/2023</t>
+  </si>
+  <si>
+    <t>5695003896</t>
   </si>
   <si>
     <t>Sense fornecedores</t>
   </si>
   <si>
-    <t>23615</t>
+    <t>5695852646</t>
   </si>
   <si>
     <t>DIFA no total das notas</t>
   </si>
   <si>
-    <t>23612</t>
+    <t>5695859343</t>
   </si>
   <si>
     <t>INSUMOS INDIRETOS DE USINAGEM</t>
   </si>
   <si>
-    <t>23611</t>
+    <t>5695878207</t>
   </si>
   <si>
     <t>Cálculo diferencial de alíquotas</t>
   </si>
   <si>
-    <t>23573</t>
+    <t>5695969947</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Campo Novo - Adição ao Patrimônio</t>
   </si>
   <si>
-    <t>23579</t>
+    <t>5695956160</t>
   </si>
   <si>
     <t>Ordens de Inspeção Usinagem</t>
   </si>
   <si>
-    <t>23561</t>
+    <t>5695989543</t>
   </si>
   <si>
     <t>Alteração Registro de Moldagem USE</t>
@@ -333,19 +363,19 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>23527</t>
+    <t>5696017484</t>
   </si>
   <si>
     <t>RELATÓRIO ESTOQUE_DEPOSITO_FABRIL_SEQUENCIAS_30112023</t>
   </si>
   <si>
-    <t>23533</t>
+    <t>5696025370</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Exportação Imobilizado para Benner</t>
   </si>
   <si>
-    <t>23759</t>
+    <t>5705230639</t>
   </si>
   <si>
     <t>Correção</t>
@@ -354,37 +384,31 @@
     <t>Altona || Sistema ERP || Integrator - Exportação Pessoas</t>
   </si>
   <si>
-    <t>23444</t>
+    <t>5608962468</t>
   </si>
   <si>
     <t>Melhoria sistema PCP</t>
   </si>
   <si>
-    <t>23101</t>
+    <t>5610924669</t>
   </si>
   <si>
     <t>TICKET LINK PARA OTFS</t>
   </si>
   <si>
-    <t>23260</t>
+    <t>5712006263</t>
   </si>
   <si>
     <t>Data Retorno Usinagem</t>
   </si>
   <si>
-    <t>19/12/2023</t>
-  </si>
-  <si>
-    <t>22503</t>
+    <t>5727873253</t>
   </si>
   <si>
     <t>Criar campos na base de conjunto</t>
   </si>
   <si>
-    <t>21/12/2023</t>
-  </si>
-  <si>
-    <t>23410</t>
+    <t>5702722114</t>
   </si>
   <si>
     <t>[MELHORIA / IMPLATAÇÃO NIMBI] - Bloqueio Condição de pagamento (Homologar)</t>
@@ -396,7 +420,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-26</t>
+    <t>Nov/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -456,6 +480,9 @@
     <t>A fazer</t>
   </si>
   <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
     <t>Abertos</t>
   </si>
   <si>
@@ -463,6 +490,9 @@
   </si>
   <si>
     <t>Baixa</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -1038,13 +1068,13 @@
         <v>33</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>36</v>
@@ -1085,13 +1115,13 @@
         <v>33</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>36</v>
@@ -1132,13 +1162,13 @@
         <v>33</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>36</v>
@@ -1179,13 +1209,13 @@
         <v>43</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>44</v>
@@ -1226,13 +1256,13 @@
         <v>47</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>44</v>
@@ -1276,10 +1306,10 @@
         <v>55</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1290,7 +1320,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1302,10 +1332,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1317,16 +1347,16 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -1337,7 +1367,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1349,10 +1379,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1364,16 +1394,16 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1384,7 +1414,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1396,10 +1426,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1414,13 +1444,13 @@
         <v>43</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>44</v>
@@ -1431,7 +1461,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1443,10 +1473,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1461,13 +1491,13 @@
         <v>47</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>44</v>
@@ -1511,10 +1541,10 @@
         <v>55</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>44</v>
@@ -1525,7 +1555,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1537,10 +1567,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1552,16 +1582,16 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>44</v>
@@ -1572,7 +1602,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1584,10 +1614,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1605,10 +1635,10 @@
         <v>24</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>44</v>
@@ -1619,7 +1649,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1631,10 +1661,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1649,13 +1679,13 @@
         <v>47</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>44</v>
@@ -1666,7 +1696,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1678,10 +1708,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1696,13 +1726,13 @@
         <v>47</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>44</v>
@@ -1713,7 +1743,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1725,10 +1755,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1743,13 +1773,13 @@
         <v>47</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>44</v>
@@ -1760,7 +1790,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1772,10 +1802,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1790,13 +1820,13 @@
         <v>47</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>44</v>
@@ -1807,7 +1837,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1819,10 +1849,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1837,13 +1867,13 @@
         <v>47</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>44</v>
@@ -1854,7 +1884,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1866,10 +1896,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1884,13 +1914,13 @@
         <v>47</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>44</v>
@@ -1901,7 +1931,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1913,10 +1943,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1931,13 +1961,13 @@
         <v>47</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>44</v>
@@ -1948,7 +1978,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1960,10 +1990,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1978,13 +2008,13 @@
         <v>47</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>44</v>
@@ -1995,7 +2025,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2007,10 +2037,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2025,13 +2055,13 @@
         <v>47</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>44</v>
@@ -2042,7 +2072,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2054,10 +2084,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2072,13 +2102,13 @@
         <v>47</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>44</v>
@@ -2089,7 +2119,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2101,10 +2131,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2119,13 +2149,13 @@
         <v>47</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>44</v>
@@ -2136,7 +2166,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2148,10 +2178,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2166,13 +2196,13 @@
         <v>47</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>44</v>
@@ -2183,7 +2213,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2195,10 +2225,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2213,13 +2243,13 @@
         <v>47</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>44</v>
@@ -2230,7 +2260,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2242,10 +2272,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2260,13 +2290,13 @@
         <v>47</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>44</v>
@@ -2277,7 +2307,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2289,10 +2319,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2307,13 +2337,13 @@
         <v>47</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>44</v>
@@ -2324,7 +2354,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2336,10 +2366,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2354,13 +2384,13 @@
         <v>47</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>44</v>
@@ -2371,7 +2401,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2383,10 +2413,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2401,13 +2431,13 @@
         <v>47</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>44</v>
@@ -2418,7 +2448,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2430,13 +2460,13 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>21</v>
@@ -2448,13 +2478,13 @@
         <v>47</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>44</v>
@@ -2465,7 +2495,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2477,10 +2507,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2495,13 +2525,13 @@
         <v>47</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>44</v>
@@ -2512,7 +2542,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2524,10 +2554,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2542,13 +2572,13 @@
         <v>47</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>44</v>
@@ -2559,22 +2589,22 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2589,13 +2619,13 @@
         <v>43</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>44</v>
@@ -2606,7 +2636,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2618,10 +2648,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2633,16 +2663,16 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>27</v>
@@ -2653,7 +2683,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2665,10 +2695,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2680,16 +2710,16 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>27</v>
@@ -2700,7 +2730,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2712,10 +2742,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2727,16 +2757,16 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>44</v>
@@ -2747,7 +2777,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2759,13 +2789,13 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>21</v>
@@ -2774,16 +2804,16 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>44</v>
@@ -2794,7 +2824,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2806,13 +2836,13 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>21</v>
@@ -2824,13 +2854,13 @@
         <v>43</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>44</v>
@@ -2852,23 +2882,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2876,16 +2906,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2896,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>892</v>
+        <v>59.9</v>
       </c>
       <c r="J5" s="4">
         <v>2</v>
@@ -2904,12 +2934,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K22">
         <v>39</v>
@@ -2917,7 +2947,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2925,7 +2955,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2956,12 +2986,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B2">
         <v>40</v>
@@ -2975,7 +3005,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>892</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2985,25 +3015,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3020,19 +3050,19 @@
         <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N10">
         <v>39</v>
@@ -3058,28 +3088,28 @@
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H11">
         <v>3</v>
       </c>
       <c r="J11" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K11">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M11" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="Q11">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -3096,33 +3126,33 @@
         <v>34</v>
       </c>
       <c r="J12" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="Q12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -3133,8 +3163,14 @@
       <c r="N13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="P13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
         <v>32</v>
       </c>
@@ -3142,15 +3178,21 @@
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
+      <c r="P14" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3158,7 +3200,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3166,7 +3208,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3174,10 +3216,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3185,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3193,16 +3235,16 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>900</v>
+        <v>944</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3213,7 +3255,7 @@
         <v>49</v>
       </c>
       <c r="F22" s="2">
-        <v>854</v>
+        <v>901</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>51</v>
@@ -3221,27 +3263,27 @@
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>31</v>
@@ -3249,13 +3291,13 @@
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -3263,72 +3305,72 @@
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="2">
+        <v>54</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
